--- a/improvement/education/plan-02.xlsx
+++ b/improvement/education/plan-02.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>500万円（従業員5人以下・カタログ注文型。特例750万円）</t>
+          <t>従業員5人以下の区分は200万円（賃上げ要件達成で300万円）。6〜20人は500万円（750万円）、21人以上は1,000万円（1,500万円）</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>35万円 = min(上限500万円, 70万円×0.5)</t>
+          <t>35万円 = min(上限200万円, 70万円×0.5)</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>min(上限500万円, 総額70万円×補助率0.5)</t>
+          <t>min(上限200万円, 総額70万円×補助率0.5)</t>
         </is>
       </c>
     </row>
